--- a/bd3.xlsx
+++ b/bd3.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="253">
   <si>
     <t>INDICADORES</t>
   </si>
@@ -624,12 +624,6 @@
   </si>
   <si>
     <t>CASO 214</t>
-  </si>
-  <si>
-    <t>CASO 215</t>
-  </si>
-  <si>
-    <t>CASO 216</t>
   </si>
   <si>
     <t>CASO 219</t>
@@ -1224,7 +1218,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1232,13 +1226,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:HX20"/>
+  <dimension ref="A1:HV20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="41.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:232" s="3" customFormat="1" ht="36" customHeight="1">
+    <row r="1" spans="1:230" s="3" customFormat="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1929,16 +1923,10 @@
       <c r="HV1" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="HW1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="HX1" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="2" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="B2" s="9">
         <v>14.65</v>
@@ -2532,111 +2520,105 @@
         <v>12.68</v>
       </c>
       <c r="GQ2" s="9">
-        <v>14.23</v>
+        <v>15.780000000000001</v>
       </c>
       <c r="GR2" s="9">
-        <v>14.9</v>
+        <v>15.33</v>
       </c>
       <c r="GS2" s="9">
-        <v>15.780000000000001</v>
+        <v>13.790000000000001</v>
       </c>
       <c r="GT2" s="9">
-        <v>15.33</v>
+        <v>15.17</v>
       </c>
       <c r="GU2" s="9">
-        <v>13.790000000000001</v>
+        <v>17.23</v>
       </c>
       <c r="GV2" s="9">
-        <v>15.17</v>
+        <v>17.8</v>
       </c>
       <c r="GW2" s="9">
-        <v>17.23</v>
+        <v>14</v>
       </c>
       <c r="GX2" s="9">
-        <v>17.8</v>
+        <v>11.301569808910495</v>
       </c>
       <c r="GY2" s="9">
+        <v>11.318063582019157</v>
+      </c>
+      <c r="GZ2" s="9">
+        <v>11.146967544332417</v>
+      </c>
+      <c r="HA2" s="9">
+        <v>10.676271654767957</v>
+      </c>
+      <c r="HB2" s="9">
+        <v>10.844552012023724</v>
+      </c>
+      <c r="HC2" s="9">
+        <v>10.423723977059275</v>
+      </c>
+      <c r="HD2" s="9">
+        <v>10.327006239134228</v>
+      </c>
+      <c r="HE2" s="9">
+        <v>10.466514280793564</v>
+      </c>
+      <c r="HF2" s="9">
+        <v>10.81</v>
+      </c>
+      <c r="HG2" s="9">
+        <v>10.54</v>
+      </c>
+      <c r="HH2" s="9">
+        <v>10.99</v>
+      </c>
+      <c r="HI2" s="9">
+        <v>10.98</v>
+      </c>
+      <c r="HJ2" s="9">
+        <v>11.05</v>
+      </c>
+      <c r="HK2" s="9">
+        <v>11.32</v>
+      </c>
+      <c r="HL2" s="9">
+        <v>11.56</v>
+      </c>
+      <c r="HM2" s="9">
+        <v>14.35</v>
+      </c>
+      <c r="HN2" s="9">
+        <v>14.35</v>
+      </c>
+      <c r="HO2" s="9">
+        <v>14.36</v>
+      </c>
+      <c r="HP2" s="9">
+        <v>14.06</v>
+      </c>
+      <c r="HQ2" s="9">
+        <v>13.72</v>
+      </c>
+      <c r="HR2" s="9">
+        <v>14.11</v>
+      </c>
+      <c r="HS2" s="9">
+        <v>14.17</v>
+      </c>
+      <c r="HT2" s="9">
         <v>14</v>
-      </c>
-      <c r="GZ2" s="9">
-        <v>11.301569808910495</v>
-      </c>
-      <c r="HA2" s="9">
-        <v>11.318063582019157</v>
-      </c>
-      <c r="HB2" s="9">
-        <v>11.146967544332417</v>
-      </c>
-      <c r="HC2" s="9">
-        <v>10.676271654767957</v>
-      </c>
-      <c r="HD2" s="9">
-        <v>10.844552012023724</v>
-      </c>
-      <c r="HE2" s="9">
-        <v>10.423723977059275</v>
-      </c>
-      <c r="HF2" s="9">
-        <v>10.327006239134228</v>
-      </c>
-      <c r="HG2" s="9">
-        <v>10.466514280793564</v>
-      </c>
-      <c r="HH2" s="9">
-        <v>10.81</v>
-      </c>
-      <c r="HI2" s="9">
-        <v>10.54</v>
-      </c>
-      <c r="HJ2" s="9">
-        <v>10.99</v>
-      </c>
-      <c r="HK2" s="9">
-        <v>10.98</v>
-      </c>
-      <c r="HL2" s="9">
-        <v>11.05</v>
-      </c>
-      <c r="HM2" s="9">
-        <v>11.32</v>
-      </c>
-      <c r="HN2" s="9">
-        <v>11.56</v>
-      </c>
-      <c r="HO2" s="9">
-        <v>14.35</v>
-      </c>
-      <c r="HP2" s="9">
-        <v>14.35</v>
-      </c>
-      <c r="HQ2" s="9">
-        <v>14.36</v>
-      </c>
-      <c r="HR2" s="9">
-        <v>14.06</v>
-      </c>
-      <c r="HS2" s="9">
-        <v>13.72</v>
-      </c>
-      <c r="HT2" s="9">
-        <v>14.11</v>
       </c>
       <c r="HU2" s="9">
         <v>14.17</v>
       </c>
       <c r="HV2" s="9">
-        <v>14</v>
-      </c>
-      <c r="HW2" s="9">
-        <v>14.17</v>
-      </c>
-      <c r="HX2" s="9">
         <v>14.13</v>
       </c>
     </row>
-    <row r="3" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="3" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B3" s="9">
         <v>9</v>
@@ -3230,111 +3212,105 @@
         <v>4.2300000000000004</v>
       </c>
       <c r="GQ3" s="9">
-        <v>11.23</v>
+        <v>8.15</v>
       </c>
       <c r="GR3" s="9">
-        <v>9.67</v>
+        <v>5.97</v>
       </c>
       <c r="GS3" s="9">
-        <v>8.15</v>
+        <v>5.44</v>
       </c>
       <c r="GT3" s="9">
-        <v>5.97</v>
+        <v>9.49</v>
       </c>
       <c r="GU3" s="9">
-        <v>5.44</v>
+        <v>5.59</v>
       </c>
       <c r="GV3" s="9">
-        <v>9.49</v>
+        <v>5.12</v>
       </c>
       <c r="GW3" s="9">
-        <v>5.59</v>
+        <v>4.38</v>
       </c>
       <c r="GX3" s="9">
-        <v>5.12</v>
+        <v>7.53</v>
       </c>
       <c r="GY3" s="9">
-        <v>4.38</v>
+        <v>7.54</v>
       </c>
       <c r="GZ3" s="9">
+        <v>7.62</v>
+      </c>
+      <c r="HA3" s="9">
+        <v>7.67</v>
+      </c>
+      <c r="HB3" s="9">
+        <v>7.7</v>
+      </c>
+      <c r="HC3" s="9">
+        <v>7.66</v>
+      </c>
+      <c r="HD3" s="9">
+        <v>7.47</v>
+      </c>
+      <c r="HE3" s="9">
+        <v>7.11</v>
+      </c>
+      <c r="HF3" s="9">
+        <v>6.83</v>
+      </c>
+      <c r="HG3" s="9">
+        <v>6.85</v>
+      </c>
+      <c r="HH3" s="9">
+        <v>6.54</v>
+      </c>
+      <c r="HI3" s="9">
+        <v>6.49</v>
+      </c>
+      <c r="HJ3" s="9">
+        <v>6.44</v>
+      </c>
+      <c r="HK3" s="9">
+        <v>6.37</v>
+      </c>
+      <c r="HL3" s="9">
+        <v>6.34</v>
+      </c>
+      <c r="HM3" s="9">
+        <v>7.87</v>
+      </c>
+      <c r="HN3" s="9">
+        <v>7.87</v>
+      </c>
+      <c r="HO3" s="9">
+        <v>7.84</v>
+      </c>
+      <c r="HP3" s="9">
+        <v>7.82</v>
+      </c>
+      <c r="HQ3" s="9">
+        <v>7.8</v>
+      </c>
+      <c r="HR3" s="9">
+        <v>7.54</v>
+      </c>
+      <c r="HS3" s="9">
+        <v>7.54</v>
+      </c>
+      <c r="HT3" s="9">
         <v>7.53</v>
       </c>
-      <c r="HA3" s="9">
-        <v>7.54</v>
-      </c>
-      <c r="HB3" s="9">
-        <v>7.62</v>
-      </c>
-      <c r="HC3" s="9">
-        <v>7.67</v>
-      </c>
-      <c r="HD3" s="9">
-        <v>7.7</v>
-      </c>
-      <c r="HE3" s="9">
-        <v>7.66</v>
-      </c>
-      <c r="HF3" s="9">
-        <v>7.47</v>
-      </c>
-      <c r="HG3" s="9">
-        <v>7.11</v>
-      </c>
-      <c r="HH3" s="9">
-        <v>6.83</v>
-      </c>
-      <c r="HI3" s="9">
-        <v>6.85</v>
-      </c>
-      <c r="HJ3" s="9">
-        <v>6.54</v>
-      </c>
-      <c r="HK3" s="9">
-        <v>6.49</v>
-      </c>
-      <c r="HL3" s="9">
-        <v>6.44</v>
-      </c>
-      <c r="HM3" s="9">
-        <v>6.37</v>
-      </c>
-      <c r="HN3" s="9">
-        <v>6.34</v>
-      </c>
-      <c r="HO3" s="9">
-        <v>7.87</v>
-      </c>
-      <c r="HP3" s="9">
-        <v>7.87</v>
-      </c>
-      <c r="HQ3" s="9">
-        <v>7.84</v>
-      </c>
-      <c r="HR3" s="9">
-        <v>7.82</v>
-      </c>
-      <c r="HS3" s="9">
-        <v>7.8</v>
-      </c>
-      <c r="HT3" s="9">
-        <v>7.54</v>
-      </c>
       <c r="HU3" s="9">
-        <v>7.54</v>
+        <v>7.29</v>
       </c>
       <c r="HV3" s="9">
-        <v>7.53</v>
-      </c>
-      <c r="HW3" s="9">
-        <v>7.29</v>
-      </c>
-      <c r="HX3" s="9">
         <v>7.37</v>
       </c>
     </row>
-    <row r="4" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="4" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B4" s="9">
         <v>4.43</v>
@@ -3928,111 +3904,105 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="GQ4" s="9">
-        <v>4.8899999999999997</v>
+        <v>4.2</v>
       </c>
       <c r="GR4" s="9">
-        <v>4.24</v>
+        <v>8.15</v>
       </c>
       <c r="GS4" s="9">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="GT4" s="9">
-        <v>8.15</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="GU4" s="9">
-        <v>7.8</v>
+        <v>7.21</v>
       </c>
       <c r="GV4" s="9">
-        <v>9.5299999999999994</v>
+        <v>6.88</v>
       </c>
       <c r="GW4" s="9">
-        <v>7.21</v>
+        <v>4.67</v>
       </c>
       <c r="GX4" s="9">
-        <v>6.88</v>
+        <v>10.7</v>
       </c>
       <c r="GY4" s="9">
-        <v>4.67</v>
+        <v>11.27</v>
       </c>
       <c r="GZ4" s="9">
-        <v>10.7</v>
+        <v>12.22</v>
       </c>
       <c r="HA4" s="9">
-        <v>11.27</v>
+        <v>12.55</v>
       </c>
       <c r="HB4" s="9">
-        <v>12.22</v>
+        <v>13.18</v>
       </c>
       <c r="HC4" s="9">
-        <v>12.55</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="HD4" s="9">
-        <v>13.18</v>
+        <v>9.93</v>
       </c>
       <c r="HE4" s="9">
-        <v>9.3699999999999992</v>
+        <v>10.09</v>
       </c>
       <c r="HF4" s="9">
-        <v>9.93</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="HG4" s="9">
-        <v>10.09</v>
+        <v>10.44</v>
       </c>
       <c r="HH4" s="9">
-        <v>10.199999999999999</v>
+        <v>11.69</v>
       </c>
       <c r="HI4" s="9">
-        <v>10.44</v>
+        <v>12.19</v>
       </c>
       <c r="HJ4" s="9">
-        <v>11.69</v>
+        <v>12.9</v>
       </c>
       <c r="HK4" s="9">
-        <v>12.19</v>
+        <v>13.38</v>
       </c>
       <c r="HL4" s="9">
-        <v>12.9</v>
+        <v>13.77</v>
       </c>
       <c r="HM4" s="9">
-        <v>13.38</v>
+        <v>10.8</v>
       </c>
       <c r="HN4" s="9">
-        <v>13.77</v>
+        <v>10.8</v>
       </c>
       <c r="HO4" s="9">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="HP4" s="9">
-        <v>10.8</v>
+        <v>11.52</v>
       </c>
       <c r="HQ4" s="9">
-        <v>11.1</v>
+        <v>12.16</v>
       </c>
       <c r="HR4" s="9">
-        <v>11.52</v>
+        <v>12.28</v>
       </c>
       <c r="HS4" s="9">
-        <v>12.16</v>
+        <v>12.94</v>
       </c>
       <c r="HT4" s="9">
-        <v>12.28</v>
+        <v>13.49</v>
       </c>
       <c r="HU4" s="9">
-        <v>12.94</v>
+        <v>13.94</v>
       </c>
       <c r="HV4" s="9">
-        <v>13.49</v>
-      </c>
-      <c r="HW4" s="9">
-        <v>13.94</v>
-      </c>
-      <c r="HX4" s="9">
         <v>14.53</v>
       </c>
     </row>
-    <row r="5" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="5" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B5" s="9">
         <v>3.2223045030563737</v>
@@ -4626,111 +4596,105 @@
         <v>3.1417917132454281</v>
       </c>
       <c r="GQ5" s="9">
-        <v>3.7428301172371343</v>
+        <v>3.2942509143688339</v>
       </c>
       <c r="GR5" s="9">
-        <v>3.7179437278810803</v>
+        <v>7.0982625794421645</v>
       </c>
       <c r="GS5" s="9">
-        <v>3.2942509143688339</v>
+        <v>7.028169724931999</v>
       </c>
       <c r="GT5" s="9">
-        <v>7.0982625794421645</v>
+        <v>8.2353403572113386</v>
       </c>
       <c r="GU5" s="9">
-        <v>7.028169724931999</v>
+        <v>6.2375659719416259</v>
       </c>
       <c r="GV5" s="9">
-        <v>8.2353403572113386</v>
+        <v>5.8527443251412263</v>
       </c>
       <c r="GW5" s="9">
-        <v>6.2375659719416259</v>
+        <v>3.1781234446034583</v>
       </c>
       <c r="GX5" s="9">
-        <v>5.8527443251412263</v>
+        <v>10.75</v>
       </c>
       <c r="GY5" s="9">
-        <v>3.1781234446034583</v>
+        <v>11.34</v>
       </c>
       <c r="GZ5" s="9">
-        <v>10.75</v>
+        <v>12.19</v>
       </c>
       <c r="HA5" s="9">
-        <v>11.34</v>
+        <v>12.49</v>
       </c>
       <c r="HB5" s="9">
-        <v>12.19</v>
+        <v>13.13</v>
       </c>
       <c r="HC5" s="9">
-        <v>12.49</v>
+        <v>9.4</v>
       </c>
       <c r="HD5" s="9">
-        <v>13.13</v>
+        <v>9.99</v>
       </c>
       <c r="HE5" s="9">
-        <v>9.4</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="HF5" s="9">
-        <v>9.99</v>
+        <v>10.23</v>
       </c>
       <c r="HG5" s="9">
-        <v>10.119999999999999</v>
+        <v>10.49</v>
       </c>
       <c r="HH5" s="9">
-        <v>10.23</v>
+        <v>11.73</v>
       </c>
       <c r="HI5" s="9">
-        <v>10.49</v>
+        <v>12.23</v>
       </c>
       <c r="HJ5" s="9">
-        <v>11.73</v>
+        <v>12.95</v>
       </c>
       <c r="HK5" s="9">
-        <v>12.23</v>
+        <v>13.43</v>
       </c>
       <c r="HL5" s="9">
-        <v>12.95</v>
+        <v>13.83</v>
       </c>
       <c r="HM5" s="9">
-        <v>13.43</v>
+        <v>10.85</v>
       </c>
       <c r="HN5" s="9">
-        <v>13.83</v>
+        <v>10.85</v>
       </c>
       <c r="HO5" s="9">
-        <v>10.85</v>
+        <v>11.15</v>
       </c>
       <c r="HP5" s="9">
-        <v>10.85</v>
+        <v>11.57</v>
       </c>
       <c r="HQ5" s="9">
-        <v>11.15</v>
+        <v>12.21</v>
       </c>
       <c r="HR5" s="9">
-        <v>11.57</v>
+        <v>12.33</v>
       </c>
       <c r="HS5" s="9">
-        <v>12.21</v>
+        <v>12.78</v>
       </c>
       <c r="HT5" s="9">
-        <v>12.33</v>
+        <v>10.928765661718101</v>
       </c>
       <c r="HU5" s="9">
-        <v>12.78</v>
+        <v>11.622335693691838</v>
       </c>
       <c r="HV5" s="9">
-        <v>10.928765661718101</v>
-      </c>
-      <c r="HW5" s="9">
-        <v>11.622335693691838</v>
-      </c>
-      <c r="HX5" s="9">
         <v>11.83601470663679</v>
       </c>
     </row>
-    <row r="6" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="6" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B6" s="9">
         <v>4.25</v>
@@ -5324,111 +5288,105 @@
         <v>4.6100000000000003</v>
       </c>
       <c r="GQ6" s="9">
-        <v>4.91</v>
+        <v>4.2</v>
       </c>
       <c r="GR6" s="9">
-        <v>4.1500000000000004</v>
+        <v>8.17</v>
       </c>
       <c r="GS6" s="9">
-        <v>4.2</v>
+        <v>7.68</v>
       </c>
       <c r="GT6" s="9">
-        <v>8.17</v>
+        <v>9.34</v>
       </c>
       <c r="GU6" s="9">
-        <v>7.68</v>
+        <v>7.11</v>
       </c>
       <c r="GV6" s="9">
-        <v>9.34</v>
+        <v>6.87</v>
       </c>
       <c r="GW6" s="9">
-        <v>7.11</v>
+        <v>4.66</v>
       </c>
       <c r="GX6" s="9">
-        <v>6.87</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="GY6" s="9">
-        <v>4.66</v>
+        <v>8.32</v>
       </c>
       <c r="GZ6" s="9">
-        <v>8.8699999999999992</v>
+        <v>14.78</v>
       </c>
       <c r="HA6" s="9">
-        <v>8.32</v>
+        <v>18.21</v>
       </c>
       <c r="HB6" s="9">
-        <v>14.78</v>
+        <v>18.78</v>
       </c>
       <c r="HC6" s="9">
-        <v>18.21</v>
+        <v>5.12</v>
       </c>
       <c r="HD6" s="9">
-        <v>18.78</v>
+        <v>2.9</v>
       </c>
       <c r="HE6" s="9">
-        <v>5.12</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="HF6" s="9">
-        <v>2.9</v>
+        <v>5.28</v>
       </c>
       <c r="HG6" s="9">
-        <v>5.1100000000000003</v>
+        <v>3.76</v>
       </c>
       <c r="HH6" s="9">
-        <v>5.28</v>
+        <v>4.43</v>
       </c>
       <c r="HI6" s="9">
-        <v>3.76</v>
+        <v>4.58</v>
       </c>
       <c r="HJ6" s="9">
-        <v>4.43</v>
+        <v>4.04</v>
       </c>
       <c r="HK6" s="9">
-        <v>4.58</v>
+        <v>4.18</v>
       </c>
       <c r="HL6" s="9">
-        <v>4.04</v>
+        <v>4.72</v>
       </c>
       <c r="HM6" s="9">
-        <v>4.18</v>
+        <v>3.43</v>
       </c>
       <c r="HN6" s="9">
-        <v>4.72</v>
+        <v>3.43</v>
       </c>
       <c r="HO6" s="9">
-        <v>3.43</v>
+        <v>3.53</v>
       </c>
       <c r="HP6" s="9">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="HQ6" s="9">
-        <v>3.53</v>
+        <v>4.54</v>
       </c>
       <c r="HR6" s="9">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="HS6" s="9">
-        <v>4.54</v>
+        <v>38.86</v>
       </c>
       <c r="HT6" s="9">
-        <v>4.45</v>
+        <v>13.53</v>
       </c>
       <c r="HU6" s="9">
-        <v>38.86</v>
+        <v>13.99</v>
       </c>
       <c r="HV6" s="9">
-        <v>13.53</v>
-      </c>
-      <c r="HW6" s="9">
-        <v>13.99</v>
-      </c>
-      <c r="HX6" s="9">
         <v>14.58</v>
       </c>
     </row>
-    <row r="7" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="7" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B7" s="9">
         <v>10.24</v>
@@ -6022,111 +5980,105 @@
         <v>7.17</v>
       </c>
       <c r="GQ7" s="9">
-        <v>1.35</v>
+        <v>6.86</v>
       </c>
       <c r="GR7" s="9">
-        <v>33.799999999999997</v>
+        <v>0</v>
       </c>
       <c r="GS7" s="9">
-        <v>6.86</v>
+        <v>100</v>
       </c>
       <c r="GT7" s="9">
-        <v>0</v>
+        <v>37.58</v>
       </c>
       <c r="GU7" s="9">
-        <v>100</v>
+        <v>53.27</v>
       </c>
       <c r="GV7" s="9">
-        <v>37.58</v>
+        <v>44.02</v>
       </c>
       <c r="GW7" s="9">
-        <v>53.27</v>
+        <v>5.16</v>
       </c>
       <c r="GX7" s="9">
-        <v>44.02</v>
+        <v>113.44</v>
       </c>
       <c r="GY7" s="9">
-        <v>5.16</v>
+        <v>110.31</v>
       </c>
       <c r="GZ7" s="9">
-        <v>113.44</v>
+        <v>104.93</v>
       </c>
       <c r="HA7" s="9">
-        <v>110.31</v>
+        <v>104.2</v>
       </c>
       <c r="HB7" s="9">
-        <v>104.93</v>
+        <v>102.46</v>
       </c>
       <c r="HC7" s="9">
-        <v>104.2</v>
+        <v>99.42</v>
       </c>
       <c r="HD7" s="9">
-        <v>102.46</v>
+        <v>95.97</v>
       </c>
       <c r="HE7" s="9">
-        <v>99.42</v>
+        <v>97.31</v>
       </c>
       <c r="HF7" s="9">
-        <v>95.97</v>
+        <v>99.26</v>
       </c>
       <c r="HG7" s="9">
-        <v>97.31</v>
+        <v>99.19</v>
       </c>
       <c r="HH7" s="9">
-        <v>99.26</v>
+        <v>99.87</v>
       </c>
       <c r="HI7" s="9">
-        <v>99.19</v>
+        <v>98.9</v>
       </c>
       <c r="HJ7" s="9">
-        <v>99.87</v>
+        <v>94.96</v>
       </c>
       <c r="HK7" s="9">
-        <v>98.9</v>
+        <v>97.4</v>
       </c>
       <c r="HL7" s="9">
-        <v>94.96</v>
+        <v>96.67</v>
       </c>
       <c r="HM7" s="9">
-        <v>97.4</v>
+        <v>134.31</v>
       </c>
       <c r="HN7" s="9">
-        <v>96.67</v>
+        <v>134.31</v>
       </c>
       <c r="HO7" s="9">
-        <v>134.31</v>
+        <v>131.46</v>
       </c>
       <c r="HP7" s="9">
-        <v>134.31</v>
+        <v>129.27000000000001</v>
       </c>
       <c r="HQ7" s="9">
-        <v>131.46</v>
+        <v>123.87</v>
       </c>
       <c r="HR7" s="9">
-        <v>129.27000000000001</v>
+        <v>120.59</v>
       </c>
       <c r="HS7" s="9">
-        <v>123.87</v>
+        <v>117.17</v>
       </c>
       <c r="HT7" s="9">
-        <v>120.59</v>
+        <v>5.32</v>
       </c>
       <c r="HU7" s="9">
-        <v>117.17</v>
+        <v>5.49</v>
       </c>
       <c r="HV7" s="9">
-        <v>5.32</v>
-      </c>
-      <c r="HW7" s="9">
-        <v>5.49</v>
-      </c>
-      <c r="HX7" s="9">
         <v>5.66</v>
       </c>
     </row>
-    <row r="8" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="8" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B8" s="9">
         <v>183.77</v>
@@ -6720,111 +6672,105 @@
         <v>129.56</v>
       </c>
       <c r="GQ8" s="9">
-        <v>143.67000000000002</v>
+        <v>177.09</v>
       </c>
       <c r="GR8" s="9">
-        <v>201.98000000000002</v>
+        <v>117.18</v>
       </c>
       <c r="GS8" s="9">
-        <v>177.09</v>
+        <v>112.06</v>
       </c>
       <c r="GT8" s="9">
-        <v>117.18</v>
+        <v>154.97</v>
       </c>
       <c r="GU8" s="9">
-        <v>112.06</v>
+        <v>113.18</v>
       </c>
       <c r="GV8" s="9">
-        <v>154.97</v>
+        <v>156.99</v>
       </c>
       <c r="GW8" s="9">
-        <v>113.18</v>
+        <v>135.85</v>
       </c>
       <c r="GX8" s="9">
-        <v>156.99</v>
+        <v>13.87</v>
       </c>
       <c r="GY8" s="9">
-        <v>135.85</v>
+        <v>14.49</v>
       </c>
       <c r="GZ8" s="9">
-        <v>13.87</v>
+        <v>15.47</v>
       </c>
       <c r="HA8" s="9">
-        <v>14.49</v>
+        <v>16.09</v>
       </c>
       <c r="HB8" s="9">
-        <v>15.47</v>
+        <v>16.7</v>
       </c>
       <c r="HC8" s="9">
-        <v>16.09</v>
+        <v>13.43</v>
       </c>
       <c r="HD8" s="9">
-        <v>16.7</v>
+        <v>13.67</v>
       </c>
       <c r="HE8" s="9">
-        <v>13.43</v>
+        <v>13.64</v>
       </c>
       <c r="HF8" s="9">
-        <v>13.67</v>
+        <v>13.66</v>
       </c>
       <c r="HG8" s="9">
-        <v>13.64</v>
+        <v>13.75</v>
       </c>
       <c r="HH8" s="9">
-        <v>13.66</v>
+        <v>15.31</v>
       </c>
       <c r="HI8" s="9">
-        <v>13.75</v>
+        <v>15.81</v>
       </c>
       <c r="HJ8" s="9">
-        <v>15.31</v>
+        <v>16.47</v>
       </c>
       <c r="HK8" s="9">
-        <v>15.81</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="HL8" s="9">
-        <v>16.47</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="HM8" s="9">
-        <v>17.079999999999998</v>
+        <v>15.21</v>
       </c>
       <c r="HN8" s="9">
-        <v>17.489999999999998</v>
+        <v>15.21</v>
       </c>
       <c r="HO8" s="9">
-        <v>15.21</v>
+        <v>15.32</v>
       </c>
       <c r="HP8" s="9">
-        <v>15.21</v>
+        <v>15.89</v>
       </c>
       <c r="HQ8" s="9">
-        <v>15.32</v>
+        <v>17</v>
       </c>
       <c r="HR8" s="9">
-        <v>15.89</v>
+        <v>17.32</v>
       </c>
       <c r="HS8" s="9">
-        <v>17</v>
+        <v>17.79</v>
       </c>
       <c r="HT8" s="9">
-        <v>17.32</v>
+        <v>113.02</v>
       </c>
       <c r="HU8" s="9">
-        <v>17.79</v>
+        <v>111.19</v>
       </c>
       <c r="HV8" s="9">
-        <v>113.02</v>
-      </c>
-      <c r="HW8" s="9">
-        <v>111.19</v>
-      </c>
-      <c r="HX8" s="9">
         <v>107.23</v>
       </c>
     </row>
-    <row r="9" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="9" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B9" s="9">
         <v>9.3137705926912364</v>
@@ -7418,111 +7364,105 @@
         <v>14.049829092652038</v>
       </c>
       <c r="GQ9" s="9">
-        <v>6.6103759849319736</v>
+        <v>10.659056688438564</v>
       </c>
       <c r="GR9" s="9">
-        <v>7.4337059090018487</v>
+        <v>12.698629830804126</v>
       </c>
       <c r="GS9" s="9">
-        <v>10.659056688438564</v>
+        <v>16.81062791391583</v>
       </c>
       <c r="GT9" s="9">
-        <v>12.698629830804126</v>
+        <v>9.10812543248535</v>
       </c>
       <c r="GU9" s="9">
-        <v>16.81062791391583</v>
+        <v>8.6162246259447652</v>
       </c>
       <c r="GV9" s="9">
-        <v>9.10812543248535</v>
+        <v>9.228817528446239</v>
       </c>
       <c r="GW9" s="9">
-        <v>8.6162246259447652</v>
+        <v>13.517927189573086</v>
       </c>
       <c r="GX9" s="9">
-        <v>9.228817528446239</v>
+        <v>12.863492288409194</v>
       </c>
       <c r="GY9" s="9">
-        <v>13.517927189573086</v>
+        <v>12.8943491174978</v>
       </c>
       <c r="GZ9" s="9">
-        <v>12.863492288409194</v>
+        <v>12.805949635017495</v>
       </c>
       <c r="HA9" s="9">
-        <v>12.8943491174978</v>
+        <v>12.723179077582369</v>
       </c>
       <c r="HB9" s="9">
-        <v>12.805949635017495</v>
+        <v>12.590381793590236</v>
       </c>
       <c r="HC9" s="9">
-        <v>12.723179077582369</v>
+        <v>12.199286451934178</v>
       </c>
       <c r="HD9" s="9">
-        <v>12.590381793590236</v>
+        <v>12.159616278047194</v>
       </c>
       <c r="HE9" s="9">
-        <v>12.199286451934178</v>
+        <v>12.062161030737968</v>
       </c>
       <c r="HF9" s="9">
-        <v>12.159616278047194</v>
+        <v>12.017266395061471</v>
       </c>
       <c r="HG9" s="9">
-        <v>12.062161030737968</v>
+        <v>11.900830724675433</v>
       </c>
       <c r="HH9" s="9">
-        <v>12.017266395061471</v>
+        <v>11.77</v>
       </c>
       <c r="HI9" s="9">
-        <v>11.900830724675433</v>
+        <v>11.79</v>
       </c>
       <c r="HJ9" s="9">
-        <v>11.77</v>
+        <v>11.82</v>
       </c>
       <c r="HK9" s="9">
-        <v>11.79</v>
+        <v>12</v>
       </c>
       <c r="HL9" s="9">
-        <v>11.82</v>
+        <v>12.082230619541235</v>
       </c>
       <c r="HM9" s="9">
-        <v>12</v>
+        <v>12.630437752905138</v>
       </c>
       <c r="HN9" s="9">
-        <v>12.082230619541235</v>
+        <v>12.630437752905138</v>
       </c>
       <c r="HO9" s="9">
-        <v>12.630437752905138</v>
+        <v>12.866037590103069</v>
       </c>
       <c r="HP9" s="9">
-        <v>12.630437752905138</v>
+        <v>13.183659043600542</v>
       </c>
       <c r="HQ9" s="9">
-        <v>12.866037590103069</v>
+        <v>13.360926441116927</v>
       </c>
       <c r="HR9" s="9">
-        <v>13.183659043600542</v>
+        <v>13.569059910955355</v>
       </c>
       <c r="HS9" s="9">
-        <v>13.360926441116927</v>
+        <v>13.80441343565546</v>
       </c>
       <c r="HT9" s="9">
-        <v>13.569059910955355</v>
+        <v>14.029130869218484</v>
       </c>
       <c r="HU9" s="9">
-        <v>13.80441343565546</v>
+        <v>14.232350300924887</v>
       </c>
       <c r="HV9" s="9">
-        <v>14.029130869218484</v>
-      </c>
-      <c r="HW9" s="9">
-        <v>14.232350300924887</v>
-      </c>
-      <c r="HX9" s="9">
         <v>14.34992288796437</v>
       </c>
     </row>
-    <row r="10" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="10" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B10" s="9">
         <v>59.320018675653685</v>
@@ -8116,111 +8056,105 @@
         <v>66.791921546944138</v>
       </c>
       <c r="GQ10" s="9">
-        <v>48.970607632919958</v>
+        <v>64.377696381734765</v>
       </c>
       <c r="GR10" s="9">
-        <v>53.4783971968562</v>
+        <v>81.623689408109072</v>
       </c>
       <c r="GS10" s="9">
-        <v>64.377696381734765</v>
+        <v>78.887392253364808</v>
       </c>
       <c r="GT10" s="9">
-        <v>81.623689408109072</v>
+        <v>57.718889617909277</v>
       </c>
       <c r="GU10" s="9">
-        <v>78.887392253364808</v>
+        <v>61.735464058513777</v>
       </c>
       <c r="GV10" s="9">
-        <v>57.718889617909277</v>
+        <v>60.073054159343585</v>
       </c>
       <c r="GW10" s="9">
-        <v>61.735464058513777</v>
+        <v>61.549910985103921</v>
       </c>
       <c r="GX10" s="9">
-        <v>60.073054159343585</v>
+        <v>82.000643315599618</v>
       </c>
       <c r="GY10" s="9">
-        <v>61.549910985103921</v>
+        <v>81.76696291452275</v>
       </c>
       <c r="GZ10" s="9">
-        <v>82.000643315599618</v>
+        <v>81.687555765512059</v>
       </c>
       <c r="HA10" s="9">
-        <v>81.76696291452275</v>
+        <v>81.619862159233833</v>
       </c>
       <c r="HB10" s="9">
-        <v>81.687555765512059</v>
+        <v>80.973251701213528</v>
       </c>
       <c r="HC10" s="9">
-        <v>81.619862159233833</v>
+        <v>79.240343876348064</v>
       </c>
       <c r="HD10" s="9">
-        <v>80.973251701213528</v>
+        <v>78.761193784575994</v>
       </c>
       <c r="HE10" s="9">
-        <v>79.240343876348064</v>
+        <v>78.216296407265204</v>
       </c>
       <c r="HF10" s="9">
-        <v>78.761193784575994</v>
+        <v>77.990657388870119</v>
       </c>
       <c r="HG10" s="9">
-        <v>78.216296407265204</v>
+        <v>76.709566046201743</v>
       </c>
       <c r="HH10" s="9">
-        <v>77.990657388870119</v>
+        <v>77.09</v>
       </c>
       <c r="HI10" s="9">
-        <v>76.709566046201743</v>
+        <v>76.930000000000007</v>
       </c>
       <c r="HJ10" s="9">
-        <v>77.09</v>
+        <v>77.73</v>
       </c>
       <c r="HK10" s="9">
-        <v>76.930000000000007</v>
+        <v>77.180000000000007</v>
       </c>
       <c r="HL10" s="9">
-        <v>77.73</v>
+        <v>77.437095265234063</v>
       </c>
       <c r="HM10" s="9">
-        <v>77.180000000000007</v>
+        <v>79.267397177011375</v>
       </c>
       <c r="HN10" s="9">
-        <v>77.437095265234063</v>
+        <v>79.267397177011375</v>
       </c>
       <c r="HO10" s="9">
-        <v>79.267397177011375</v>
+        <v>80.271625468237744</v>
       </c>
       <c r="HP10" s="9">
-        <v>79.267397177011375</v>
+        <v>81.652802275653855</v>
       </c>
       <c r="HQ10" s="9">
-        <v>80.271625468237744</v>
+        <v>82.521067980382384</v>
       </c>
       <c r="HR10" s="9">
-        <v>81.652802275653855</v>
+        <v>81.350550492870653</v>
       </c>
       <c r="HS10" s="9">
-        <v>82.521067980382384</v>
+        <v>81.766614426293259</v>
       </c>
       <c r="HT10" s="9">
-        <v>81.350550492870653</v>
+        <v>81.741005516595791</v>
       </c>
       <c r="HU10" s="9">
-        <v>81.766614426293259</v>
+        <v>83.067167415221761</v>
       </c>
       <c r="HV10" s="9">
-        <v>81.741005516595791</v>
-      </c>
-      <c r="HW10" s="9">
-        <v>83.067167415221761</v>
-      </c>
-      <c r="HX10" s="9">
         <v>83.079276040801048</v>
       </c>
     </row>
-    <row r="11" spans="1:232" s="6" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="1:230" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B11" s="9">
         <v>18.781437525746185</v>
@@ -8814,111 +8748,105 @@
         <v>24.960199318909027</v>
       </c>
       <c r="GQ11" s="9">
-        <v>18.161784452723936</v>
+        <v>19.659483853473088</v>
       </c>
       <c r="GR11" s="9">
-        <v>17.991030889216002</v>
+        <v>21.240565870333683</v>
       </c>
       <c r="GS11" s="9">
-        <v>19.659483853473088</v>
+        <v>26.806675775139954</v>
       </c>
       <c r="GT11" s="9">
-        <v>21.240565870333683</v>
+        <v>20.945471367273928</v>
       </c>
       <c r="GU11" s="9">
-        <v>26.806675775139954</v>
+        <v>18.272374938006468</v>
       </c>
       <c r="GV11" s="9">
-        <v>20.945471367273928</v>
+        <v>18.99644600696022</v>
       </c>
       <c r="GW11" s="9">
-        <v>18.272374938006468</v>
+        <v>25.384715429146155</v>
       </c>
       <c r="GX11" s="9">
-        <v>18.99644600696022</v>
+        <v>23.938697342559852</v>
       </c>
       <c r="GY11" s="9">
-        <v>25.384715429146155</v>
+        <v>23.812971766822315</v>
       </c>
       <c r="GZ11" s="9">
-        <v>23.938697342559852</v>
+        <v>23.655569555341803</v>
       </c>
       <c r="HA11" s="9">
-        <v>23.812971766822315</v>
+        <v>23.493422382014018</v>
       </c>
       <c r="HB11" s="9">
-        <v>23.655569555341803</v>
+        <v>23.327746642774638</v>
       </c>
       <c r="HC11" s="9">
-        <v>23.493422382014018</v>
+        <v>22.852106766355284</v>
       </c>
       <c r="HD11" s="9">
-        <v>23.327746642774638</v>
+        <v>22.694241283455359</v>
       </c>
       <c r="HE11" s="9">
-        <v>22.852106766355284</v>
+        <v>22.626818761552105</v>
       </c>
       <c r="HF11" s="9">
-        <v>22.694241283455359</v>
+        <v>22.580576264444581</v>
       </c>
       <c r="HG11" s="9">
-        <v>22.626818761552105</v>
+        <v>22.597411279196844</v>
       </c>
       <c r="HH11" s="9">
-        <v>22.580576264444581</v>
+        <v>22.22</v>
       </c>
       <c r="HI11" s="9">
-        <v>22.597411279196844</v>
+        <v>22.31</v>
       </c>
       <c r="HJ11" s="9">
-        <v>22.22</v>
+        <v>22.18</v>
       </c>
       <c r="HK11" s="9">
-        <v>22.31</v>
+        <v>22.46</v>
       </c>
       <c r="HL11" s="9">
-        <v>22.18</v>
+        <v>22.512761626159037</v>
       </c>
       <c r="HM11" s="9">
-        <v>22.46</v>
+        <v>22.971450781940526</v>
       </c>
       <c r="HN11" s="9">
-        <v>22.512761626159037</v>
+        <v>22.971450781940526</v>
       </c>
       <c r="HO11" s="9">
-        <v>22.971450781940526</v>
+        <v>23.173761270633285</v>
       </c>
       <c r="HP11" s="9">
-        <v>22.971450781940526</v>
+        <v>23.356387022491237</v>
       </c>
       <c r="HQ11" s="9">
-        <v>23.173761270633285</v>
+        <v>23.415567723606785</v>
       </c>
       <c r="HR11" s="9">
-        <v>23.356387022491237</v>
+        <v>24.045044817007138</v>
       </c>
       <c r="HS11" s="9">
-        <v>23.415567723606785</v>
+        <v>24.202894731546298</v>
       </c>
       <c r="HT11" s="9">
-        <v>24.045044817007138</v>
+        <v>24.381642271808811</v>
       </c>
       <c r="HU11" s="9">
-        <v>24.202894731546298</v>
+        <v>24.343005787788506</v>
       </c>
       <c r="HV11" s="9">
-        <v>24.381642271808811</v>
-      </c>
-      <c r="HW11" s="9">
-        <v>24.343005787788506</v>
-      </c>
-      <c r="HX11" s="9">
         <v>24.529612987179505</v>
       </c>
     </row>
-    <row r="12" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="12" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B12" s="9">
         <v>1105.3619132353815</v>
@@ -9512,111 +9440,105 @@
         <v>999.32917633064505</v>
       </c>
       <c r="GQ12" s="9">
-        <v>1904.8529803625988</v>
+        <v>1124.5162095691489</v>
       </c>
       <c r="GR12" s="9">
-        <v>1417.7901650970766</v>
+        <v>854.81382133333329</v>
       </c>
       <c r="GS12" s="9">
-        <v>1124.5162095691489</v>
+        <v>565.06979252595147</v>
       </c>
       <c r="GT12" s="9">
-        <v>854.81382133333329</v>
+        <v>1548.9740131215667</v>
       </c>
       <c r="GU12" s="9">
-        <v>565.06979252595147</v>
+        <v>1098.9605815797318</v>
       </c>
       <c r="GV12" s="9">
-        <v>1548.9740131215667</v>
+        <v>1246.6870583916382</v>
       </c>
       <c r="GW12" s="9">
-        <v>1098.9605815797318</v>
+        <v>1082.8081913786407</v>
       </c>
       <c r="GX12" s="9">
-        <v>1246.6870583916382</v>
+        <v>724.43681316666664</v>
       </c>
       <c r="GY12" s="9">
-        <v>1082.8081913786407</v>
+        <v>726.83511387959868</v>
       </c>
       <c r="GZ12" s="9">
-        <v>724.43681316666664</v>
+        <v>713.43816841584157</v>
       </c>
       <c r="HA12" s="9">
-        <v>726.83511387959868</v>
+        <v>723.14185730000008</v>
       </c>
       <c r="HB12" s="9">
-        <v>713.43816841584157</v>
+        <v>720.06959520134228</v>
       </c>
       <c r="HC12" s="9">
-        <v>723.14185730000008</v>
+        <v>708.37691911032027</v>
       </c>
       <c r="HD12" s="9">
-        <v>720.06959520134228</v>
+        <v>741.36092959409586</v>
       </c>
       <c r="HE12" s="9">
-        <v>708.37691911032027</v>
+        <v>750.44692106617651</v>
       </c>
       <c r="HF12" s="9">
-        <v>741.36092959409586</v>
+        <v>751.49041724264714</v>
       </c>
       <c r="HG12" s="9">
-        <v>750.44692106617651</v>
+        <v>730.33842961130745</v>
       </c>
       <c r="HH12" s="9">
-        <v>751.49041724264714</v>
+        <v>698.53</v>
       </c>
       <c r="HI12" s="9">
-        <v>730.33842961130745</v>
+        <v>650.82000000000005</v>
       </c>
       <c r="HJ12" s="9">
-        <v>698.53</v>
+        <v>654.29999999999995</v>
       </c>
       <c r="HK12" s="9">
-        <v>650.82000000000005</v>
+        <v>664.53</v>
       </c>
       <c r="HL12" s="9">
-        <v>654.29999999999995</v>
+        <v>649.67973282894741</v>
       </c>
       <c r="HM12" s="9">
-        <v>664.53</v>
+        <v>588.6406848124999</v>
       </c>
       <c r="HN12" s="9">
-        <v>649.67973282894741</v>
+        <v>588.6406848124999</v>
       </c>
       <c r="HO12" s="9">
-        <v>588.6406848124999</v>
+        <v>604.87122568690086</v>
       </c>
       <c r="HP12" s="9">
-        <v>588.6406848124999</v>
+        <v>602.50289389937109</v>
       </c>
       <c r="HQ12" s="9">
-        <v>604.87122568690086</v>
+        <v>604.40627968553451</v>
       </c>
       <c r="HR12" s="9">
-        <v>602.50289389937109</v>
+        <v>645.8578722261484</v>
       </c>
       <c r="HS12" s="9">
-        <v>604.40627968553451</v>
+        <v>647.31705392857145</v>
       </c>
       <c r="HT12" s="9">
-        <v>645.8578722261484</v>
+        <v>655.51442832142857</v>
       </c>
       <c r="HU12" s="9">
-        <v>647.31705392857145</v>
+        <v>604.18225888157895</v>
       </c>
       <c r="HV12" s="9">
-        <v>655.51442832142857</v>
-      </c>
-      <c r="HW12" s="9">
-        <v>604.18225888157895</v>
-      </c>
-      <c r="HX12" s="9">
         <v>605.85537097087376</v>
       </c>
     </row>
-    <row r="13" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="13" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B13" s="9">
         <v>28211.850649166667</v>
@@ -10210,111 +10132,105 @@
         <v>13768.535318333334</v>
       </c>
       <c r="GQ13" s="9">
-        <v>46201.188581741073</v>
+        <v>32524.468830615388</v>
       </c>
       <c r="GR13" s="9">
-        <v>41796.82716973684</v>
+        <v>15303.924865806452</v>
       </c>
       <c r="GS13" s="9">
-        <v>32524.468830615388</v>
+        <v>12561.936156923077</v>
       </c>
       <c r="GT13" s="9">
-        <v>15303.924865806452</v>
+        <v>29083.202658923765</v>
       </c>
       <c r="GU13" s="9">
-        <v>12561.936156923077</v>
+        <v>24580.085008000002</v>
       </c>
       <c r="GV13" s="9">
-        <v>29083.202658923765</v>
+        <v>27830.804427333333</v>
       </c>
       <c r="GW13" s="9">
-        <v>24580.085008000002</v>
+        <v>15490.172737777777</v>
       </c>
       <c r="GX13" s="9">
-        <v>27830.804427333333</v>
+        <v>15523.64599642857</v>
       </c>
       <c r="GY13" s="9">
-        <v>15490.172737777777</v>
+        <v>15523.121360714287</v>
       </c>
       <c r="GZ13" s="9">
-        <v>15523.64599642857</v>
+        <v>15440.840359285714</v>
       </c>
       <c r="HA13" s="9">
-        <v>15523.121360714287</v>
+        <v>15495.896942142857</v>
       </c>
       <c r="HB13" s="9">
-        <v>15440.840359285714</v>
+        <v>15327.195669285715</v>
       </c>
       <c r="HC13" s="9">
-        <v>15495.896942142857</v>
+        <v>14218.136733571429</v>
       </c>
       <c r="HD13" s="9">
-        <v>15327.195669285715</v>
+        <v>14350.629422857141</v>
       </c>
       <c r="HE13" s="9">
-        <v>14218.136733571429</v>
+        <v>14580.111609285714</v>
       </c>
       <c r="HF13" s="9">
-        <v>14350.629422857141</v>
+        <v>14600.385249285715</v>
       </c>
       <c r="HG13" s="9">
-        <v>14580.111609285714</v>
+        <v>14763.269684285715</v>
       </c>
       <c r="HH13" s="9">
-        <v>14600.385249285715</v>
+        <v>14369.66</v>
       </c>
       <c r="HI13" s="9">
-        <v>14763.269684285715</v>
+        <v>14271.63</v>
       </c>
       <c r="HJ13" s="9">
-        <v>14369.66</v>
+        <v>14347.79</v>
       </c>
       <c r="HK13" s="9">
-        <v>14271.63</v>
+        <v>14144.93</v>
       </c>
       <c r="HL13" s="9">
-        <v>14347.79</v>
+        <v>14107.331341428573</v>
       </c>
       <c r="HM13" s="9">
-        <v>14144.93</v>
+        <v>13454.644224285712</v>
       </c>
       <c r="HN13" s="9">
-        <v>14107.331341428573</v>
+        <v>13454.644224285712</v>
       </c>
       <c r="HO13" s="9">
-        <v>13454.644224285712</v>
+        <v>13523.192402857141</v>
       </c>
       <c r="HP13" s="9">
-        <v>13454.644224285712</v>
+        <v>13685.422875714285</v>
       </c>
       <c r="HQ13" s="9">
-        <v>13523.192402857141</v>
+        <v>13728.656924285713</v>
       </c>
       <c r="HR13" s="9">
-        <v>13685.422875714285</v>
+        <v>13055.555560000001</v>
       </c>
       <c r="HS13" s="9">
-        <v>13728.656924285713</v>
+        <v>12946.341078571428</v>
       </c>
       <c r="HT13" s="9">
-        <v>13055.555560000001</v>
+        <v>13110.288566428571</v>
       </c>
       <c r="HU13" s="9">
-        <v>12946.341078571428</v>
+        <v>13119.386192857142</v>
       </c>
       <c r="HV13" s="9">
-        <v>13110.288566428571</v>
-      </c>
-      <c r="HW13" s="9">
-        <v>13119.386192857142</v>
-      </c>
-      <c r="HX13" s="9">
         <v>13372.093545</v>
       </c>
     </row>
-    <row r="14" spans="1:232" s="5" customFormat="1" ht="15" customHeight="1">
+    <row r="14" spans="1:230" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B14" s="9">
         <v>97.9</v>
@@ -10908,111 +10824,105 @@
         <v>103.13</v>
       </c>
       <c r="GQ14" s="9">
-        <v>85.88</v>
+        <v>92.26</v>
       </c>
       <c r="GR14" s="9">
-        <v>86.8</v>
+        <v>93.8</v>
       </c>
       <c r="GS14" s="9">
-        <v>92.26</v>
+        <v>102.55</v>
       </c>
       <c r="GT14" s="9">
-        <v>93.8</v>
+        <v>95.86</v>
       </c>
       <c r="GU14" s="9">
-        <v>102.55</v>
+        <v>98.98</v>
       </c>
       <c r="GV14" s="9">
-        <v>95.86</v>
+        <v>85.87</v>
       </c>
       <c r="GW14" s="9">
-        <v>98.98</v>
+        <v>96.09</v>
       </c>
       <c r="GX14" s="9">
-        <v>85.87</v>
+        <v>112.67</v>
       </c>
       <c r="GY14" s="9">
-        <v>96.09</v>
+        <v>112.5</v>
       </c>
       <c r="GZ14" s="9">
-        <v>112.67</v>
+        <v>113.89</v>
       </c>
       <c r="HA14" s="9">
-        <v>112.5</v>
+        <v>114.27</v>
       </c>
       <c r="HB14" s="9">
-        <v>113.89</v>
+        <v>116.34</v>
       </c>
       <c r="HC14" s="9">
-        <v>114.27</v>
+        <v>125.53</v>
       </c>
       <c r="HD14" s="9">
-        <v>116.34</v>
+        <v>120.7</v>
       </c>
       <c r="HE14" s="9">
-        <v>125.53</v>
+        <v>112.9</v>
       </c>
       <c r="HF14" s="9">
-        <v>120.7</v>
+        <v>108.35</v>
       </c>
       <c r="HG14" s="9">
-        <v>112.9</v>
+        <v>107.04</v>
       </c>
       <c r="HH14" s="9">
-        <v>108.35</v>
+        <v>105.51</v>
       </c>
       <c r="HI14" s="9">
-        <v>107.04</v>
+        <v>104.5</v>
       </c>
       <c r="HJ14" s="9">
-        <v>105.51</v>
+        <v>103.84</v>
       </c>
       <c r="HK14" s="9">
-        <v>104.5</v>
+        <v>104.43</v>
       </c>
       <c r="HL14" s="9">
-        <v>103.84</v>
+        <v>104.32</v>
       </c>
       <c r="HM14" s="9">
-        <v>104.43</v>
+        <v>105.45</v>
       </c>
       <c r="HN14" s="9">
-        <v>104.32</v>
+        <v>105.45</v>
       </c>
       <c r="HO14" s="9">
-        <v>105.45</v>
+        <v>103.96</v>
       </c>
       <c r="HP14" s="9">
-        <v>105.45</v>
+        <v>102.38</v>
       </c>
       <c r="HQ14" s="9">
-        <v>103.96</v>
+        <v>101.8</v>
       </c>
       <c r="HR14" s="9">
-        <v>102.38</v>
+        <v>104.06</v>
       </c>
       <c r="HS14" s="9">
-        <v>101.8</v>
+        <v>104.78</v>
       </c>
       <c r="HT14" s="9">
-        <v>104.06</v>
+        <v>103.59</v>
       </c>
       <c r="HU14" s="9">
-        <v>104.78</v>
+        <v>100.16</v>
       </c>
       <c r="HV14" s="9">
-        <v>103.59</v>
-      </c>
-      <c r="HW14" s="9">
-        <v>100.16</v>
-      </c>
-      <c r="HX14" s="9">
         <v>99.42</v>
       </c>
     </row>
-    <row r="15" spans="1:232" s="6" customFormat="1" ht="15" customHeight="1">
+    <row r="15" spans="1:230" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B15" s="9">
         <v>19.321813445369649</v>
@@ -11606,111 +11516,105 @@
         <v>14.150348229111071</v>
       </c>
       <c r="GQ15" s="9">
-        <v>14.637347227527631</v>
+        <v>13.043569821958487</v>
       </c>
       <c r="GR15" s="9">
-        <v>20.230099194524339</v>
+        <v>3.7206685231115761</v>
       </c>
       <c r="GS15" s="9">
-        <v>13.043569821958487</v>
+        <v>14.182276552022923</v>
       </c>
       <c r="GT15" s="9">
-        <v>3.7206685231115761</v>
+        <v>13.670015483510065</v>
       </c>
       <c r="GU15" s="9">
-        <v>14.182276552022923</v>
+        <v>13.133018489315129</v>
       </c>
       <c r="GV15" s="9">
-        <v>13.670015483510065</v>
+        <v>8.9684979531095905</v>
       </c>
       <c r="GW15" s="9">
-        <v>13.133018489315129</v>
+        <v>27.281587464089235</v>
       </c>
       <c r="GX15" s="9">
-        <v>8.9684979531095905</v>
+        <v>-8.109991560805387</v>
       </c>
       <c r="GY15" s="9">
-        <v>27.281587464089235</v>
+        <v>-6.4853961709316916</v>
       </c>
       <c r="GZ15" s="9">
-        <v>-8.109991560805387</v>
+        <v>-6.7603808839487769</v>
       </c>
       <c r="HA15" s="9">
-        <v>-6.4853961709316916</v>
+        <v>-6.9995395082697627</v>
       </c>
       <c r="HB15" s="9">
-        <v>-6.7603808839487769</v>
+        <v>-5.1997968255224132</v>
       </c>
       <c r="HC15" s="9">
-        <v>-6.9995395082697627</v>
+        <v>-7.6702453220369158</v>
       </c>
       <c r="HD15" s="9">
-        <v>-5.1997968255224132</v>
+        <v>-7.4887036271958056</v>
       </c>
       <c r="HE15" s="9">
-        <v>-7.6702453220369158</v>
+        <v>-7.8891861645487422</v>
       </c>
       <c r="HF15" s="9">
-        <v>-7.4887036271958056</v>
+        <v>-7.7434532770428337</v>
       </c>
       <c r="HG15" s="9">
-        <v>-7.8891861645487422</v>
+        <v>-0.18092708527171672</v>
       </c>
       <c r="HH15" s="9">
-        <v>-7.7434532770428337</v>
+        <v>-1.63</v>
       </c>
       <c r="HI15" s="9">
-        <v>-0.18092708527171672</v>
+        <v>-2.09</v>
       </c>
       <c r="HJ15" s="9">
-        <v>-1.63</v>
+        <v>-2.44</v>
       </c>
       <c r="HK15" s="9">
-        <v>-2.09</v>
+        <v>-2.0099999999999998</v>
       </c>
       <c r="HL15" s="9">
-        <v>-2.44</v>
+        <v>-1.9038653494715574</v>
       </c>
       <c r="HM15" s="9">
-        <v>-2.0099999999999998</v>
+        <v>-1.4552616948786286</v>
       </c>
       <c r="HN15" s="9">
-        <v>-1.9038653494715574</v>
+        <v>-1.4552616948786286</v>
       </c>
       <c r="HO15" s="9">
-        <v>-1.4552616948786286</v>
+        <v>-1.4575013394689289</v>
       </c>
       <c r="HP15" s="9">
-        <v>-1.4552616948786286</v>
+        <v>-1.2209002064258245</v>
       </c>
       <c r="HQ15" s="9">
-        <v>-1.4575013394689289</v>
+        <v>-2.234713207345095</v>
       </c>
       <c r="HR15" s="9">
-        <v>-1.2209002064258245</v>
+        <v>0.78894430241817182</v>
       </c>
       <c r="HS15" s="9">
-        <v>-2.234713207345095</v>
+        <v>1.260415437897684</v>
       </c>
       <c r="HT15" s="9">
-        <v>0.78894430241817182</v>
+        <v>1.595824235531786</v>
       </c>
       <c r="HU15" s="9">
-        <v>1.260415437897684</v>
+        <v>1.2154525535649188</v>
       </c>
       <c r="HV15" s="9">
-        <v>1.595824235531786</v>
-      </c>
-      <c r="HW15" s="9">
-        <v>1.2154525535649188</v>
-      </c>
-      <c r="HX15" s="9">
         <v>0.66233935205759231</v>
       </c>
     </row>
-    <row r="16" spans="1:232" s="6" customFormat="1" ht="15" customHeight="1">
+    <row r="16" spans="1:230" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B16" s="9">
         <v>2.3160030624681074</v>
@@ -12304,111 +12208,105 @@
         <v>1.9055773658091111</v>
       </c>
       <c r="GQ16" s="9">
-        <v>1.3586253210997181</v>
+        <v>1.6644870414716857</v>
       </c>
       <c r="GR16" s="9">
-        <v>2.2680911869654237</v>
+        <v>0.49621175867655021</v>
       </c>
       <c r="GS16" s="9">
-        <v>1.6644870414716857</v>
+        <v>1.9046103532834768</v>
       </c>
       <c r="GT16" s="9">
-        <v>0.49621175867655021</v>
+        <v>1.207082079121462</v>
       </c>
       <c r="GU16" s="9">
-        <v>1.9046103532834768</v>
+        <v>2.167618935820641</v>
       </c>
       <c r="GV16" s="9">
-        <v>1.207082079121462</v>
+        <v>1.524646873926476</v>
       </c>
       <c r="GW16" s="9">
-        <v>2.167618935820641</v>
+        <v>3.7396169506757704</v>
       </c>
       <c r="GX16" s="9">
-        <v>1.524646873926476</v>
+        <v>-0.95868351308621369</v>
       </c>
       <c r="GY16" s="9">
-        <v>3.7396169506757704</v>
+        <v>-0.75888344306389766</v>
       </c>
       <c r="GZ16" s="9">
-        <v>-0.95868351308621369</v>
+        <v>-0.78241652996155864</v>
       </c>
       <c r="HA16" s="9">
-        <v>-0.75888344306389766</v>
+        <v>-0.80203362961535052</v>
       </c>
       <c r="HB16" s="9">
-        <v>-0.78241652996155864</v>
+        <v>-0.59153639851411099</v>
       </c>
       <c r="HC16" s="9">
-        <v>-0.80203362961535052</v>
+        <v>-0.86322894294610863</v>
       </c>
       <c r="HD16" s="9">
-        <v>-0.59153639851411099</v>
+        <v>-0.84105279168147185</v>
       </c>
       <c r="HE16" s="9">
-        <v>-0.86322894294610863</v>
+        <v>-0.88685549739544789</v>
       </c>
       <c r="HF16" s="9">
-        <v>-0.84105279168147185</v>
+        <v>-0.87418185073490606</v>
       </c>
       <c r="HG16" s="9">
-        <v>-0.88685549739544789</v>
+        <v>-2.0656189936118865E-2</v>
       </c>
       <c r="HH16" s="9">
-        <v>-0.87418185073490606</v>
+        <v>-0.19</v>
       </c>
       <c r="HI16" s="9">
-        <v>-2.0656189936118865E-2</v>
+        <v>-0.25</v>
       </c>
       <c r="HJ16" s="9">
-        <v>-0.19</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="HK16" s="9">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="HL16" s="9">
-        <v>-0.28999999999999998</v>
+        <v>-0.23195483934582589</v>
       </c>
       <c r="HM16" s="9">
-        <v>-0.24</v>
+        <v>-0.18285437992479142</v>
       </c>
       <c r="HN16" s="9">
-        <v>-0.23195483934582589</v>
+        <v>-0.18285437992479142</v>
       </c>
       <c r="HO16" s="9">
-        <v>-0.18285437992479142</v>
+        <v>-0.18582499100263261</v>
       </c>
       <c r="HP16" s="9">
-        <v>-0.18285437992479142</v>
+        <v>-0.15857105169534544</v>
       </c>
       <c r="HQ16" s="9">
-        <v>-0.18582499100263261</v>
+        <v>-0.29251192622375582</v>
       </c>
       <c r="HR16" s="9">
-        <v>-0.15857105169534544</v>
+        <v>0.10517802404309146</v>
       </c>
       <c r="HS16" s="9">
-        <v>-0.29251192622375582</v>
+        <v>0.16949757083150996</v>
       </c>
       <c r="HT16" s="9">
-        <v>0.10517802404309146</v>
+        <v>0.21637732608319632</v>
       </c>
       <c r="HU16" s="9">
-        <v>0.16949757083150996</v>
+        <v>0.16637486307269916</v>
       </c>
       <c r="HV16" s="9">
-        <v>0.21637732608319632</v>
-      </c>
-      <c r="HW16" s="9">
-        <v>0.16637486307269916</v>
-      </c>
-      <c r="HX16" s="9">
         <v>9.1396780057740518E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:232" s="6" customFormat="1" ht="15" customHeight="1">
+    <row r="17" spans="1:230" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B17" s="9">
         <v>22.92</v>
@@ -13002,111 +12900,105 @@
         <v>22.07</v>
       </c>
       <c r="GQ17" s="9">
-        <v>18.260000000000002</v>
+        <v>25.79</v>
       </c>
       <c r="GR17" s="9">
-        <v>22.18</v>
+        <v>21.97</v>
       </c>
       <c r="GS17" s="9">
-        <v>25.79</v>
+        <v>18.13</v>
       </c>
       <c r="GT17" s="9">
-        <v>21.97</v>
+        <v>21.240000000000002</v>
       </c>
       <c r="GU17" s="9">
-        <v>18.13</v>
+        <v>21.32</v>
       </c>
       <c r="GV17" s="9">
-        <v>21.240000000000002</v>
+        <v>22.47</v>
       </c>
       <c r="GW17" s="9">
-        <v>21.32</v>
+        <v>17.03</v>
       </c>
       <c r="GX17" s="9">
-        <v>22.47</v>
+        <v>39.270000000000003</v>
       </c>
       <c r="GY17" s="9">
-        <v>17.03</v>
+        <v>40.08</v>
       </c>
       <c r="GZ17" s="9">
-        <v>39.270000000000003</v>
+        <v>40.54</v>
       </c>
       <c r="HA17" s="9">
-        <v>40.08</v>
+        <v>41.35</v>
       </c>
       <c r="HB17" s="9">
-        <v>40.54</v>
+        <v>43.02</v>
       </c>
       <c r="HC17" s="9">
-        <v>41.35</v>
+        <v>45.31</v>
       </c>
       <c r="HD17" s="9">
-        <v>43.02</v>
+        <v>46.09</v>
       </c>
       <c r="HE17" s="9">
-        <v>45.31</v>
+        <v>40.32</v>
       </c>
       <c r="HF17" s="9">
-        <v>46.09</v>
+        <v>34.659999999999997</v>
       </c>
       <c r="HG17" s="9">
-        <v>40.32</v>
+        <v>32.92</v>
       </c>
       <c r="HH17" s="9">
-        <v>34.659999999999997</v>
+        <v>32.659999999999997</v>
       </c>
       <c r="HI17" s="9">
-        <v>32.92</v>
+        <v>30.66</v>
       </c>
       <c r="HJ17" s="9">
-        <v>32.659999999999997</v>
+        <v>30.57</v>
       </c>
       <c r="HK17" s="9">
-        <v>30.66</v>
+        <v>30.06</v>
       </c>
       <c r="HL17" s="9">
-        <v>30.57</v>
+        <v>31.26</v>
       </c>
       <c r="HM17" s="9">
+        <v>28.27</v>
+      </c>
+      <c r="HN17" s="9">
+        <v>28.27</v>
+      </c>
+      <c r="HO17" s="9">
+        <v>27.09</v>
+      </c>
+      <c r="HP17" s="9">
+        <v>33.07</v>
+      </c>
+      <c r="HQ17" s="9">
+        <v>30.97</v>
+      </c>
+      <c r="HR17" s="9">
+        <v>31.67</v>
+      </c>
+      <c r="HS17" s="9">
+        <v>33.049999999999997</v>
+      </c>
+      <c r="HT17" s="9">
+        <v>35.04</v>
+      </c>
+      <c r="HU17" s="9">
+        <v>32.74</v>
+      </c>
+      <c r="HV17" s="9">
         <v>30.06</v>
       </c>
-      <c r="HN17" s="9">
-        <v>31.26</v>
-      </c>
-      <c r="HO17" s="9">
-        <v>28.27</v>
-      </c>
-      <c r="HP17" s="9">
-        <v>28.27</v>
-      </c>
-      <c r="HQ17" s="9">
-        <v>27.09</v>
-      </c>
-      <c r="HR17" s="9">
-        <v>33.07</v>
-      </c>
-      <c r="HS17" s="9">
-        <v>30.97</v>
-      </c>
-      <c r="HT17" s="9">
-        <v>31.67</v>
-      </c>
-      <c r="HU17" s="9">
-        <v>33.049999999999997</v>
-      </c>
-      <c r="HV17" s="9">
-        <v>35.04</v>
-      </c>
-      <c r="HW17" s="9">
-        <v>32.74</v>
-      </c>
-      <c r="HX17" s="9">
-        <v>30.06</v>
-      </c>
     </row>
-    <row r="18" spans="1:232" s="6" customFormat="1" ht="15" customHeight="1">
+    <row r="18" spans="1:230" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B18" s="9">
         <v>82.05</v>
@@ -13700,111 +13592,105 @@
         <v>74.78</v>
       </c>
       <c r="GQ18" s="9">
-        <v>73.23</v>
+        <v>71.83</v>
       </c>
       <c r="GR18" s="9">
-        <v>95.79</v>
+        <v>156.15</v>
       </c>
       <c r="GS18" s="9">
-        <v>71.83</v>
+        <v>97.43</v>
       </c>
       <c r="GT18" s="9">
-        <v>156.15</v>
+        <v>94.13</v>
       </c>
       <c r="GU18" s="9">
-        <v>97.43</v>
+        <v>91.54</v>
       </c>
       <c r="GV18" s="9">
-        <v>94.13</v>
+        <v>100.34</v>
       </c>
       <c r="GW18" s="9">
-        <v>91.54</v>
+        <v>71.150000000000006</v>
       </c>
       <c r="GX18" s="9">
-        <v>100.34</v>
+        <v>77.17</v>
       </c>
       <c r="GY18" s="9">
-        <v>71.150000000000006</v>
+        <v>86.32</v>
       </c>
       <c r="GZ18" s="9">
-        <v>77.17</v>
+        <v>105.74</v>
       </c>
       <c r="HA18" s="9">
-        <v>86.32</v>
+        <v>131.47</v>
       </c>
       <c r="HB18" s="9">
-        <v>105.74</v>
+        <v>135.72999999999999</v>
       </c>
       <c r="HC18" s="9">
-        <v>131.47</v>
+        <v>127.93</v>
       </c>
       <c r="HD18" s="9">
-        <v>135.72999999999999</v>
+        <v>122.28</v>
       </c>
       <c r="HE18" s="9">
-        <v>127.93</v>
+        <v>99.77</v>
       </c>
       <c r="HF18" s="9">
-        <v>122.28</v>
+        <v>98.68</v>
       </c>
       <c r="HG18" s="9">
-        <v>99.77</v>
+        <v>100.87</v>
       </c>
       <c r="HH18" s="9">
-        <v>98.68</v>
+        <v>104.19</v>
       </c>
       <c r="HI18" s="9">
-        <v>100.87</v>
+        <v>100.88</v>
       </c>
       <c r="HJ18" s="9">
-        <v>104.19</v>
+        <v>101.95</v>
       </c>
       <c r="HK18" s="9">
-        <v>100.88</v>
+        <v>115.38</v>
       </c>
       <c r="HL18" s="9">
-        <v>101.95</v>
+        <v>108.22</v>
       </c>
       <c r="HM18" s="9">
-        <v>115.38</v>
+        <v>93.11</v>
       </c>
       <c r="HN18" s="9">
-        <v>108.22</v>
+        <v>93.11</v>
       </c>
       <c r="HO18" s="9">
-        <v>93.11</v>
+        <v>89.37</v>
       </c>
       <c r="HP18" s="9">
-        <v>93.11</v>
+        <v>96.12</v>
       </c>
       <c r="HQ18" s="9">
-        <v>89.37</v>
+        <v>105.29</v>
       </c>
       <c r="HR18" s="9">
-        <v>96.12</v>
+        <v>111.27</v>
       </c>
       <c r="HS18" s="9">
-        <v>105.29</v>
+        <v>109.07</v>
       </c>
       <c r="HT18" s="9">
-        <v>111.27</v>
+        <v>113.22</v>
       </c>
       <c r="HU18" s="9">
-        <v>109.07</v>
+        <v>111.58</v>
       </c>
       <c r="HV18" s="9">
-        <v>113.22</v>
-      </c>
-      <c r="HW18" s="9">
-        <v>111.58</v>
-      </c>
-      <c r="HX18" s="9">
         <v>108.94</v>
       </c>
     </row>
-    <row r="19" spans="1:232" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="19" spans="1:230" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B19" s="9">
         <v>-1.294310265887062</v>
@@ -14398,804 +14284,792 @@
         <v>-0.15513140352452129</v>
       </c>
       <c r="GQ19" s="9">
-        <v>-1.1291955260645445</v>
+        <v>-0.1298258686259042</v>
       </c>
       <c r="GR19" s="9">
-        <v>-0.13420474338533303</v>
+        <v>-0.58176569865000283</v>
       </c>
       <c r="GS19" s="9">
-        <v>-0.1298258686259042</v>
+        <v>-0.18991955798358157</v>
       </c>
       <c r="GT19" s="9">
-        <v>-0.58176569865000283</v>
+        <v>-1.2352983923645642</v>
       </c>
       <c r="GU19" s="9">
-        <v>-0.18991955798358157</v>
+        <v>-0.74943830059685712</v>
       </c>
       <c r="GV19" s="9">
-        <v>-1.2352983923645642</v>
+        <v>2.6999498940835694E-2</v>
       </c>
       <c r="GW19" s="9">
-        <v>-0.74943830059685712</v>
+        <v>-0.55828098907140111</v>
       </c>
       <c r="GX19" s="9">
-        <v>2.6999498940835694E-2</v>
+        <v>2.7956613069491348E-2</v>
       </c>
       <c r="GY19" s="9">
-        <v>-0.55828098907140111</v>
+        <v>1.3704280132364945</v>
       </c>
       <c r="GZ19" s="9">
-        <v>2.7956613069491348E-2</v>
+        <v>1.0380966357194104</v>
       </c>
       <c r="HA19" s="9">
-        <v>1.3704280132364945</v>
+        <v>2.352311497113583</v>
       </c>
       <c r="HB19" s="9">
-        <v>1.0380966357194104</v>
+        <v>1.0560498166733594</v>
       </c>
       <c r="HC19" s="9">
-        <v>2.352311497113583</v>
+        <v>0.4778835285284907</v>
       </c>
       <c r="HD19" s="9">
-        <v>1.0560498166733594</v>
+        <v>-1.1859260659102657</v>
       </c>
       <c r="HE19" s="9">
-        <v>0.4778835285284907</v>
+        <v>-3.6560826192412303</v>
       </c>
       <c r="HF19" s="9">
-        <v>-1.1859260659102657</v>
+        <v>-3.8661437238603549</v>
       </c>
       <c r="HG19" s="9">
-        <v>-3.6560826192412303</v>
+        <v>-4.1561133586155599</v>
       </c>
       <c r="HH19" s="9">
-        <v>-3.8661437238603549</v>
+        <v>-4.33</v>
       </c>
       <c r="HI19" s="9">
-        <v>-4.1561133586155599</v>
+        <v>-5.15</v>
       </c>
       <c r="HJ19" s="9">
-        <v>-4.33</v>
+        <v>-1.3</v>
       </c>
       <c r="HK19" s="9">
-        <v>-5.15</v>
+        <v>-1.716336298359822</v>
       </c>
       <c r="HL19" s="9">
-        <v>-1.3</v>
+        <v>-3.164090980070192</v>
       </c>
       <c r="HM19" s="9">
-        <v>-1.716336298359822</v>
+        <v>-3.2763369972488099</v>
       </c>
       <c r="HN19" s="9">
-        <v>-3.164090980070192</v>
+        <v>-3.2763369972488099</v>
       </c>
       <c r="HO19" s="9">
-        <v>-3.2763369972488099</v>
+        <v>-3.5107010019548617</v>
       </c>
       <c r="HP19" s="9">
-        <v>-3.2763369972488099</v>
+        <v>-1.9776355427759773</v>
       </c>
       <c r="HQ19" s="9">
-        <v>-3.5107010019548617</v>
+        <v>-2.2419229847605631</v>
       </c>
       <c r="HR19" s="9">
-        <v>-1.9776355427759773</v>
+        <v>-0.62518946986123691</v>
       </c>
       <c r="HS19" s="9">
-        <v>-2.2419229847605631</v>
+        <v>0.33889242480142279</v>
       </c>
       <c r="HT19" s="9">
-        <v>-0.62518946986123691</v>
+        <v>0.5531256498465642</v>
       </c>
       <c r="HU19" s="9">
-        <v>0.33889242480142279</v>
+        <v>-0.28392778374411687</v>
       </c>
       <c r="HV19" s="9">
-        <v>0.5531256498465642</v>
-      </c>
-      <c r="HW19" s="9">
-        <v>-0.28392778374411687</v>
-      </c>
-      <c r="HX19" s="9">
         <v>-0.25824201450539525</v>
       </c>
     </row>
-    <row r="20" spans="1:232" s="8" customFormat="1" ht="12.75">
+    <row r="20" spans="1:230" s="8" customFormat="1" ht="12.75">
       <c r="A20" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="E20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="H20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="S20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="T20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="V20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="W20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="X20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AA20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="AB20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AC20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AD20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="AF20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AG20" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="AH20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AI20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AK20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AL20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AM20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="AN20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AO20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AP20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="AQ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AR20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AT20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AU20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AV20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AW20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AX20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="AY20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AZ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BA20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BB20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="BC20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BD20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BE20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BF20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BG20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BH20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BI20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BJ20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="BK20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BL20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BM20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BN20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="BO20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BP20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BQ20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BR20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BS20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BU20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BV20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="BW20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BX20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BY20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BZ20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="CA20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CB20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="CC20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="CD20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CE20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="CF20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CG20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CH20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="CI20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CJ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CK20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="CL20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="CM20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CN20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="CP20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CQ20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="CR20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CS20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CT20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="CU20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CV20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CW20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="CX20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="CY20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CZ20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="DA20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DB20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DC20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DD20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DE20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DF20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="DG20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DH20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DI20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DJ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DK20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="DL20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DN20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DO20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DP20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DQ20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="DR20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DS20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DT20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DU20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DV20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DW20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DX20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="DY20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DZ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EA20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EB20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="EC20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="ED20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EE20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EF20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="EG20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EH20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="EI20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EK20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="EL20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EM20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EN20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="EO20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EP20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EQ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="ER20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="ES20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="ET20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="EU20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="EV20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EW20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="EX20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EY20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="EZ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FA20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FB20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FD20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="FE20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FF20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FG20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FH20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FI20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FJ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FK20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FL20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FM20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FN20" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="FO20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FP20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FQ20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FR20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FS20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FT20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FU20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FV20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FW20" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="FX20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FY20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="FZ20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="GA20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GB20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GC20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GD20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="GE20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GF20" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="GG20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GH20" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="GI20" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="GJ20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL20" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="I20" s="7" t="s">
+      <c r="GM20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GN20" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="GO20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GP20" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="K20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="S20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="T20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="U20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="V20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="W20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="X20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="Y20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="Z20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AA20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="AB20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AC20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="AD20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="AE20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="AF20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AG20" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="AH20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="AI20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AJ20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="AK20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AL20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AM20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="AN20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AO20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="AP20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="AQ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AR20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="AS20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="AT20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AU20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="AV20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AW20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AX20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="AY20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AZ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BA20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="BB20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="BC20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BD20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="BE20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="BF20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BG20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="BH20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BI20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BJ20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="BK20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BL20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BM20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="BN20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="BO20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BP20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="BQ20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="BR20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BS20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="BT20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BU20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BV20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BX20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="BY20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="BZ20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="CA20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CB20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="CC20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="CD20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CE20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="CF20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CG20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CH20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="CI20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CJ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CK20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="CL20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="CM20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CN20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="CO20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="CP20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CQ20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="CR20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CS20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CT20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="CU20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CV20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CW20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="CX20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="CY20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="CZ20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="DA20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="DB20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DC20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="DD20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DE20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DF20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="DG20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DH20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DI20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DJ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DK20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="DL20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="DM20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DN20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="DO20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DP20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DQ20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="DR20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DS20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DT20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DU20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="DV20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DW20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="DX20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="DY20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="DZ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EA20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EB20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="EC20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="ED20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EE20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EF20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="EG20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EH20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="EI20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="EJ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EK20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="EL20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EM20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EN20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="EO20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EP20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EQ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="ER20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="ES20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="ET20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="EU20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="EV20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EW20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="EX20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EY20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="EZ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FA20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FB20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="FC20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FD20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="FE20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="FF20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FG20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="FH20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FI20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FJ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FK20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FL20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="FM20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FN20" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="FO20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="FP20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FQ20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="FR20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FS20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FT20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FU20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="FV20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FW20" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="FX20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="FY20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="FZ20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="GA20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="GB20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="GC20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="GD20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="GE20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="GF20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="GG20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="GH20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="GI20" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="GJ20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="GK20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="GL20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="GM20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="GN20" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="GO20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="GP20" s="7" t="s">
-        <v>253</v>
-      </c>
       <c r="GQ20" s="7" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="GR20" s="7" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="GS20" s="7" t="s">
         <v>251</v>
       </c>
       <c r="GT20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GU20" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="GU20" s="7" t="s">
-        <v>253</v>
-      </c>
       <c r="GV20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GW20" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="GW20" s="4" t="s">
-        <v>253</v>
-      </c>
       <c r="GX20" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="GY20" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="GZ20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HA20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HB20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HC20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HD20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HE20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HF20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HG20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HH20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HI20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HJ20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HK20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HL20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HM20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HN20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HO20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HP20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HQ20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HR20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HS20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HT20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HU20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="HV20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="HW20" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="HX20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
